--- a/Bill of Materials.xlsx
+++ b/Bill of Materials.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\groups\nordinrsrch\Kendon\OS1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B2DBE5-3D12-4BAC-BBE1-DA5EC6BB748E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71CFC8E6-25E5-4FE5-8F52-53F15F2726D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25320" yWindow="2235" windowWidth="25440" windowHeight="15270" xr2:uid="{18FE35BA-1422-49DD-9CBC-F02C04230EF8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="353">
   <si>
     <t>Designator</t>
   </si>
@@ -583,9 +583,6 @@
     <t>https://a.co/d/09OcuKCe</t>
   </si>
   <si>
-    <t xml:space="preserve">PCB MOLEX connectors </t>
-  </si>
-  <si>
     <t>https://www.digikey.com/short/ft70prjf</t>
   </si>
   <si>
@@ -1127,6 +1124,18 @@
   </si>
   <si>
     <t xml:space="preserve"> Glass slide preparation. (Item #: 179418)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-pin MOLEX connectors </t>
+  </si>
+  <si>
+    <t>Resistors</t>
+  </si>
+  <si>
+    <t>4.7 kOhm and 10 kOhm resistor</t>
+  </si>
+  <si>
+    <t>https://a.co/d/08zMVh81</t>
   </si>
 </sst>
 </file>
@@ -1504,7 +1513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A189396B-8023-47A8-ACB7-2D166A986A96}">
-  <dimension ref="A1:K160"/>
+  <dimension ref="A1:K161"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" customWidth="1"/>
@@ -1540,7 +1549,7 @@
       </c>
       <c r="H1" s="1"/>
       <c r="K1" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -1558,7 +1567,7 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -1566,8 +1575,8 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="K3">
-        <f>SUM(F5:F158)</f>
-        <v>69557.52</v>
+        <f>SUM(F5:F159)</f>
+        <v>69563.510000000009</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1581,10 +1590,10 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -1601,10 +1610,10 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -1621,10 +1630,10 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1641,7 +1650,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C8" t="s">
         <v>162</v>
@@ -1661,36 +1670,36 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E9" t="s">
         <v>139</v>
       </c>
       <c r="G9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E10" t="s">
         <v>139</v>
       </c>
       <c r="G10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1698,7 +1707,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D11" t="s">
         <v>8</v>
@@ -1715,21 +1724,21 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
+        <v>262</v>
+      </c>
+      <c r="C12" t="s">
         <v>263</v>
       </c>
-      <c r="C12" t="s">
-        <v>264</v>
-      </c>
       <c r="D12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -1749,10 +1758,10 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C14" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -1769,10 +1778,10 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1794,7 +1803,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
@@ -1814,7 +1823,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C20" t="s">
         <v>16</v>
@@ -1854,10 +1863,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>168</v>
+        <v>349</v>
       </c>
       <c r="C22" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D22">
         <v>3</v>
@@ -1877,7 +1886,7 @@
         <v>143</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D23" s="2">
         <v>6</v>
@@ -1897,7 +1906,7 @@
         <v>145</v>
       </c>
       <c r="C24" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D24">
         <v>3</v>
@@ -1914,10 +1923,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C25" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1929,15 +1938,15 @@
         <v>175</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C26" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1954,10 +1963,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C27" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1974,7 +1983,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C28" t="s">
         <v>22</v>
@@ -1994,10 +2003,10 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C29" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -2014,7 +2023,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C30" t="s">
         <v>25</v>
@@ -2034,10 +2043,10 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C31" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -2052,49 +2061,49 @@
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>350</v>
+      </c>
+      <c r="C32" t="s">
+        <v>351</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>5.99</v>
+      </c>
+      <c r="F32">
+        <v>5.99</v>
+      </c>
+      <c r="G32" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>148</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
-        <v>27</v>
-      </c>
-      <c r="C35" t="s">
-        <v>28</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="E35">
-        <v>47.22</v>
-      </c>
-      <c r="F35">
-        <v>47.22</v>
-      </c>
-      <c r="G35" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>237</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D36">
         <v>1</v>
       </c>
       <c r="E36">
-        <v>16.899999999999999</v>
+        <v>47.22</v>
       </c>
       <c r="F36">
-        <v>16.899999999999999</v>
+        <v>47.22</v>
       </c>
       <c r="G36" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2102,19 +2111,19 @@
         <v>236</v>
       </c>
       <c r="C37" t="s">
-        <v>282</v>
+        <v>30</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E37">
-        <v>3.35</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="F37">
-        <v>16.77</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="G37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2122,44 +2131,44 @@
         <v>235</v>
       </c>
       <c r="C38" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D38">
+        <v>5</v>
+      </c>
+      <c r="E38">
+        <v>3.35</v>
+      </c>
+      <c r="F38">
+        <v>16.77</v>
+      </c>
+      <c r="G38" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>234</v>
+      </c>
+      <c r="C39" t="s">
+        <v>282</v>
+      </c>
+      <c r="D39">
         <v>2</v>
       </c>
-      <c r="E38">
+      <c r="E39">
         <v>7.6</v>
       </c>
-      <c r="F38">
+      <c r="F39">
         <v>15.2</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G39" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>149</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B44" t="s">
-        <v>190</v>
-      </c>
-      <c r="C44" t="s">
-        <v>284</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="E44">
-        <v>6.38</v>
-      </c>
-      <c r="F44">
-        <v>6.38</v>
-      </c>
-      <c r="G44" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -2167,19 +2176,19 @@
         <v>189</v>
       </c>
       <c r="C45" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E45">
-        <v>12.46</v>
+        <v>6.38</v>
       </c>
       <c r="F45">
-        <v>49.9</v>
+        <v>6.38</v>
       </c>
       <c r="G45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -2187,599 +2196,599 @@
         <v>188</v>
       </c>
       <c r="C46" t="s">
-        <v>36</v>
+        <v>284</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E46">
-        <v>8.7899999999999991</v>
+        <v>12.46</v>
       </c>
       <c r="F46">
-        <v>26.37</v>
+        <v>49.9</v>
       </c>
       <c r="G46" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C47" t="s">
-        <v>286</v>
+        <v>36</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E47">
-        <v>97.5</v>
+        <v>8.7899999999999991</v>
       </c>
       <c r="F47">
-        <v>97.5</v>
+        <v>26.37</v>
       </c>
       <c r="G47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C48" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48">
-        <v>15.2</v>
+        <v>97.5</v>
       </c>
       <c r="F48">
-        <v>30.4</v>
+        <v>97.5</v>
       </c>
       <c r="G48" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C49" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49">
-        <v>6.44</v>
+        <v>15.2</v>
       </c>
       <c r="F49">
-        <v>6.44</v>
+        <v>30.4</v>
       </c>
       <c r="G49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>41</v>
+        <v>184</v>
       </c>
       <c r="C50" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="D50">
         <v>1</v>
       </c>
       <c r="E50">
-        <v>137.97999999999999</v>
+        <v>6.44</v>
       </c>
       <c r="F50">
-        <v>137.97999999999999</v>
+        <v>6.44</v>
       </c>
       <c r="G50" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>186</v>
+        <v>41</v>
       </c>
       <c r="C51" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D51">
         <v>1</v>
       </c>
       <c r="E51">
-        <v>8.98</v>
+        <v>137.97999999999999</v>
       </c>
       <c r="F51">
-        <v>8.98</v>
+        <v>137.97999999999999</v>
       </c>
       <c r="G51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C52" t="s">
+        <v>288</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52">
+        <v>8.98</v>
+      </c>
+      <c r="F52">
+        <v>8.98</v>
+      </c>
+      <c r="G52" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>186</v>
+      </c>
+      <c r="C53" t="s">
         <v>44</v>
       </c>
-      <c r="D52">
-        <v>1</v>
-      </c>
-      <c r="E52">
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53">
         <v>10.55</v>
       </c>
-      <c r="F52">
+      <c r="F53">
         <v>10.55</v>
       </c>
-      <c r="G52" t="s">
+      <c r="G53" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>150</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B56" t="s">
-        <v>46</v>
-      </c>
-      <c r="C56" t="s">
-        <v>290</v>
-      </c>
-      <c r="D56">
-        <v>1</v>
-      </c>
-      <c r="E56" s="4">
-        <v>9.33</v>
-      </c>
-      <c r="F56">
-        <v>9.33</v>
-      </c>
-      <c r="G56" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>173</v>
+        <v>46</v>
       </c>
       <c r="C57" t="s">
-        <v>291</v>
-      </c>
-      <c r="D57" s="4">
+        <v>289</v>
+      </c>
+      <c r="D57">
         <v>1</v>
       </c>
       <c r="E57" s="4">
-        <v>8.07</v>
+        <v>9.33</v>
       </c>
       <c r="F57">
-        <v>8.07</v>
+        <v>9.33</v>
       </c>
       <c r="G57" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="C58" t="s">
-        <v>292</v>
-      </c>
-      <c r="D58">
+        <v>290</v>
+      </c>
+      <c r="D58" s="4">
         <v>1</v>
       </c>
       <c r="E58" s="4">
-        <v>10.28</v>
+        <v>8.07</v>
       </c>
       <c r="F58">
-        <v>10.28</v>
+        <v>8.07</v>
       </c>
       <c r="G58" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>50</v>
+        <v>190</v>
       </c>
       <c r="C59" t="s">
-        <v>293</v>
-      </c>
-      <c r="D59" s="4">
+        <v>291</v>
+      </c>
+      <c r="D59">
         <v>1</v>
       </c>
       <c r="E59" s="4">
-        <v>12.71</v>
+        <v>10.28</v>
       </c>
       <c r="F59">
-        <v>12.71</v>
+        <v>10.28</v>
       </c>
       <c r="G59" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>192</v>
+        <v>50</v>
       </c>
       <c r="C60" t="s">
-        <v>294</v>
-      </c>
-      <c r="D60">
-        <v>4</v>
+        <v>292</v>
+      </c>
+      <c r="D60" s="4">
+        <v>1</v>
       </c>
       <c r="E60" s="4">
-        <v>8.6300000000000008</v>
+        <v>12.71</v>
       </c>
       <c r="F60">
-        <v>34.520000000000003</v>
+        <v>12.71</v>
       </c>
       <c r="G60" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="C61" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E61" s="4">
-        <v>10.3</v>
+        <v>8.6300000000000008</v>
       </c>
       <c r="F61">
-        <v>10.3</v>
+        <v>34.520000000000003</v>
       </c>
       <c r="G61" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C62" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" s="4">
-        <v>8.0299999999999994</v>
+        <v>10.3</v>
       </c>
       <c r="F62">
-        <v>16.059999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="G62" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>193</v>
+        <v>55</v>
       </c>
       <c r="C63" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" s="4">
-        <v>13.16</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="F63">
-        <v>13.16</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>298</v>
+        <v>16.059999999999999</v>
+      </c>
+      <c r="G63" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C64" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="D64">
         <v>1</v>
       </c>
       <c r="E64" s="4">
-        <v>19.3</v>
+        <v>13.16</v>
       </c>
       <c r="F64">
-        <v>19.3</v>
-      </c>
-      <c r="G64" t="s">
-        <v>57</v>
+        <v>13.16</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>58</v>
+        <v>193</v>
       </c>
       <c r="C65" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" s="4">
-        <v>8.0299999999999994</v>
+        <v>19.3</v>
       </c>
       <c r="F65">
-        <v>16.059999999999999</v>
+        <v>19.3</v>
       </c>
       <c r="G65" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C66" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" s="4">
-        <v>10.3</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="F66">
-        <v>10.3</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="G66" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
+        <v>59</v>
+      </c>
+      <c r="C67" t="s">
+        <v>302</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67" s="4">
+        <v>10.3</v>
+      </c>
+      <c r="F67">
+        <v>10.3</v>
+      </c>
+      <c r="G67" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
         <v>61</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C68" t="s">
         <v>166</v>
       </c>
-      <c r="D67">
-        <v>1</v>
-      </c>
-      <c r="E67" s="4">
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68" s="4">
         <v>6.49</v>
       </c>
-      <c r="F67">
+      <c r="F68">
         <v>6.49</v>
       </c>
-      <c r="G67" s="5" t="s">
+      <c r="G68" s="5" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
         <v>151</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B71" t="s">
-        <v>62</v>
-      </c>
-      <c r="C71" t="s">
-        <v>304</v>
-      </c>
-      <c r="D71">
-        <v>1</v>
-      </c>
-      <c r="E71">
-        <v>3392.5</v>
-      </c>
-      <c r="F71">
-        <v>3392.5</v>
-      </c>
-      <c r="G71" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C72" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D72">
         <v>1</v>
       </c>
       <c r="E72">
-        <v>3847.57</v>
+        <v>3392.5</v>
       </c>
       <c r="F72">
-        <v>3847.57</v>
+        <v>3392.5</v>
       </c>
       <c r="G72" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>170</v>
+        <v>64</v>
       </c>
       <c r="C73" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D73">
         <v>1</v>
       </c>
       <c r="E73">
-        <v>1177.03</v>
+        <v>3847.57</v>
       </c>
       <c r="F73">
-        <v>1177.03</v>
+        <v>3847.57</v>
       </c>
       <c r="G73" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>67</v>
+        <v>169</v>
       </c>
       <c r="C74" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D74">
         <v>1</v>
       </c>
       <c r="E74">
-        <v>6500</v>
+        <v>1177.03</v>
       </c>
       <c r="F74">
-        <v>6500</v>
-      </c>
-      <c r="G74" s="5" t="s">
-        <v>307</v>
+        <v>1177.03</v>
+      </c>
+      <c r="G74" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>195</v>
+        <v>67</v>
       </c>
       <c r="C75" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D75">
         <v>1</v>
       </c>
       <c r="E75">
+        <v>6500</v>
+      </c>
+      <c r="F75">
+        <v>6500</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>194</v>
+      </c>
+      <c r="C76" t="s">
+        <v>308</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76">
         <v>89.61</v>
       </c>
-      <c r="F75">
+      <c r="F76">
         <v>89.61</v>
       </c>
-      <c r="G75" t="s">
+      <c r="G76" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
         <v>152</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B80" t="s">
-        <v>196</v>
-      </c>
-      <c r="C80" t="s">
-        <v>310</v>
-      </c>
-      <c r="D80">
-        <v>1</v>
-      </c>
-      <c r="E80">
-        <v>5.95</v>
-      </c>
-      <c r="F80">
-        <v>5.95</v>
-      </c>
-      <c r="G80" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C81" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D81">
         <v>1</v>
       </c>
       <c r="E81">
-        <v>33.950000000000003</v>
+        <v>5.95</v>
       </c>
       <c r="F81">
-        <v>33.950000000000003</v>
+        <v>5.95</v>
       </c>
       <c r="G81" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C82" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82">
-        <v>9.9499999999999993</v>
+        <v>33.950000000000003</v>
       </c>
       <c r="F82">
-        <v>19.89</v>
+        <v>33.950000000000003</v>
       </c>
       <c r="G82" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C83" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83">
+        <v>9.9499999999999993</v>
+      </c>
+      <c r="F83">
+        <v>19.89</v>
+      </c>
+      <c r="G83" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>198</v>
+      </c>
+      <c r="C84" t="s">
+        <v>312</v>
+      </c>
+      <c r="D84">
+        <v>1</v>
+      </c>
+      <c r="E84">
         <v>10.95</v>
       </c>
-      <c r="F83">
+      <c r="F84">
         <v>10.95</v>
       </c>
-      <c r="G83" t="s">
+      <c r="G84" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
         <v>153</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B88" t="s">
-        <v>172</v>
-      </c>
-      <c r="C88" t="s">
-        <v>314</v>
-      </c>
-      <c r="D88">
-        <v>1</v>
-      </c>
-      <c r="E88">
-        <v>86</v>
-      </c>
-      <c r="F88">
-        <v>86</v>
-      </c>
-      <c r="G88" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -2787,212 +2796,209 @@
         <v>171</v>
       </c>
       <c r="C89" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D89">
         <v>1</v>
       </c>
       <c r="E89">
-        <v>715</v>
+        <v>86</v>
       </c>
       <c r="F89">
-        <v>715</v>
-      </c>
-      <c r="G89" s="5" t="s">
-        <v>315</v>
+        <v>86</v>
+      </c>
+      <c r="G89" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
+        <v>170</v>
+      </c>
+      <c r="C90" t="s">
+        <v>315</v>
+      </c>
+      <c r="D90">
+        <v>1</v>
+      </c>
+      <c r="E90">
+        <v>715</v>
+      </c>
+      <c r="F90">
+        <v>715</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
         <v>74</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C91" t="s">
+        <v>316</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+      <c r="E91">
+        <v>120</v>
+      </c>
+      <c r="F91">
+        <v>120</v>
+      </c>
+      <c r="G91" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="D90">
-        <v>1</v>
-      </c>
-      <c r="E90">
-        <v>120</v>
-      </c>
-      <c r="F90">
-        <v>120</v>
-      </c>
-      <c r="G90" s="5" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B96" t="s">
-        <v>200</v>
-      </c>
-      <c r="C96" t="s">
-        <v>319</v>
-      </c>
-      <c r="D96">
-        <v>2</v>
-      </c>
-      <c r="E96">
-        <v>938.6</v>
-      </c>
-      <c r="F96">
-        <v>1877.2</v>
-      </c>
-      <c r="G96" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C97" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97">
-        <v>122.03</v>
+        <v>938.6</v>
       </c>
       <c r="F97">
-        <v>122.03</v>
+        <v>1877.2</v>
       </c>
       <c r="G97" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C98" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D98">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E98">
-        <v>826.75</v>
+        <v>122.03</v>
       </c>
       <c r="F98">
-        <v>2480.25</v>
+        <v>122.03</v>
       </c>
       <c r="G98" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C99" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E99">
-        <v>662.5</v>
+        <v>826.75</v>
       </c>
       <c r="F99">
-        <v>662.5</v>
+        <v>2480.25</v>
       </c>
       <c r="G99" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C100" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D100">
         <v>1</v>
       </c>
       <c r="E100">
-        <v>360.4</v>
+        <v>662.5</v>
       </c>
       <c r="F100">
-        <v>360.4</v>
+        <v>662.5</v>
       </c>
       <c r="G100" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C101" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D101">
         <v>1</v>
       </c>
       <c r="E101">
-        <v>2100</v>
+        <v>360.4</v>
       </c>
       <c r="F101">
-        <v>2100</v>
+        <v>360.4</v>
       </c>
       <c r="G101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C102" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D102">
         <v>1</v>
       </c>
       <c r="E102">
-        <v>4800</v>
+        <v>2100</v>
       </c>
       <c r="F102">
-        <v>4800</v>
+        <v>2100</v>
       </c>
       <c r="G102" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C103" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D103">
         <v>1</v>
       </c>
       <c r="E103">
-        <v>4300</v>
+        <v>4800</v>
       </c>
       <c r="F103">
-        <v>4300</v>
+        <v>4800</v>
       </c>
       <c r="G103" t="s">
-        <v>82</v>
-      </c>
-      <c r="H103" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C104" t="s">
         <v>326</v>
@@ -3001,202 +3007,205 @@
         <v>1</v>
       </c>
       <c r="E104">
-        <v>320</v>
+        <v>4300</v>
       </c>
       <c r="F104">
-        <v>320</v>
+        <v>4300</v>
       </c>
       <c r="G104" t="s">
-        <v>84</v>
+        <v>82</v>
+      </c>
+      <c r="H104" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C105" t="s">
+        <v>325</v>
+      </c>
+      <c r="D105">
+        <v>1</v>
+      </c>
+      <c r="E105">
+        <v>320</v>
+      </c>
+      <c r="F105">
+        <v>320</v>
+      </c>
+      <c r="G105" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B106" t="s">
+        <v>208</v>
+      </c>
+      <c r="C106" t="s">
         <v>85</v>
       </c>
-      <c r="D105">
-        <v>1</v>
-      </c>
-      <c r="E105">
+      <c r="D106">
+        <v>1</v>
+      </c>
+      <c r="E106">
         <v>8.2899999999999991</v>
       </c>
-      <c r="F105">
+      <c r="F106">
         <v>8.2899999999999991</v>
       </c>
-      <c r="G105" t="s">
+      <c r="G106" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
         <v>155</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B110" t="s">
-        <v>210</v>
-      </c>
-      <c r="C110" t="s">
-        <v>328</v>
-      </c>
-      <c r="D110">
-        <v>1</v>
-      </c>
-      <c r="E110">
-        <v>381.34</v>
-      </c>
-      <c r="F110">
-        <v>381.34</v>
-      </c>
-      <c r="G110" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C111" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D111">
         <v>1</v>
       </c>
       <c r="E111">
-        <v>532.59</v>
+        <v>381.34</v>
       </c>
       <c r="F111">
-        <v>532.59</v>
+        <v>381.34</v>
       </c>
       <c r="G111" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C112" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D112">
         <v>1</v>
       </c>
       <c r="E112">
-        <v>474.23</v>
+        <v>532.59</v>
       </c>
       <c r="F112">
-        <v>474.23</v>
+        <v>532.59</v>
       </c>
       <c r="G112" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C113" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D113">
         <v>1</v>
       </c>
       <c r="E113">
+        <v>474.23</v>
+      </c>
+      <c r="F113">
+        <v>474.23</v>
+      </c>
+      <c r="G113" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B114" t="s">
+        <v>212</v>
+      </c>
+      <c r="C114" t="s">
+        <v>330</v>
+      </c>
+      <c r="D114">
+        <v>1</v>
+      </c>
+      <c r="E114">
         <v>5.99</v>
       </c>
-      <c r="F113">
+      <c r="F114">
         <v>5.99</v>
       </c>
-      <c r="G113" t="s">
+      <c r="G114" t="s">
         <v>90</v>
       </c>
-      <c r="H113" t="s">
+      <c r="H114" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
         <v>156</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B118" t="s">
-        <v>214</v>
-      </c>
-      <c r="C118" t="s">
-        <v>91</v>
-      </c>
-      <c r="D118">
-        <v>1</v>
-      </c>
-      <c r="F118">
-        <v>20000</v>
-      </c>
-      <c r="G118" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C119" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D119">
         <v>1</v>
       </c>
       <c r="F119">
-        <v>5000</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>160</v>
+        <v>20000</v>
+      </c>
+      <c r="G119" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C120" t="s">
+        <v>93</v>
+      </c>
+      <c r="D120">
+        <v>1</v>
+      </c>
+      <c r="F120">
+        <v>5000</v>
+      </c>
+      <c r="G120" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B121" t="s">
+        <v>215</v>
+      </c>
+      <c r="C121" t="s">
         <v>163</v>
       </c>
-      <c r="D120">
-        <v>1</v>
-      </c>
-      <c r="F120">
+      <c r="D121">
+        <v>1</v>
+      </c>
+      <c r="F121">
         <v>800</v>
       </c>
-      <c r="G120" t="s">
+      <c r="G121" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="1" t="s">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
         <v>157</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B124" t="s">
-        <v>182</v>
-      </c>
-      <c r="C124" t="s">
-        <v>332</v>
-      </c>
-      <c r="D124">
-        <v>1</v>
-      </c>
-      <c r="E124">
-        <v>97.63</v>
-      </c>
-      <c r="F124">
-        <v>97.63</v>
-      </c>
-      <c r="G124" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -3204,19 +3213,19 @@
         <v>181</v>
       </c>
       <c r="C125" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D125">
         <v>1</v>
       </c>
       <c r="E125">
-        <v>0.94</v>
+        <v>97.63</v>
       </c>
       <c r="F125">
-        <v>0.94</v>
+        <v>97.63</v>
       </c>
       <c r="G125" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -3224,19 +3233,19 @@
         <v>180</v>
       </c>
       <c r="C126" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D126">
         <v>1</v>
       </c>
       <c r="E126">
-        <v>2.52</v>
+        <v>0.94</v>
       </c>
       <c r="F126">
-        <v>2.52</v>
+        <v>0.94</v>
       </c>
       <c r="G126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -3244,19 +3253,19 @@
         <v>179</v>
       </c>
       <c r="C127" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D127">
         <v>1</v>
       </c>
       <c r="E127">
-        <v>5.99</v>
+        <v>2.52</v>
       </c>
       <c r="F127">
-        <v>5.99</v>
+        <v>2.52</v>
       </c>
       <c r="G127" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -3264,19 +3273,19 @@
         <v>178</v>
       </c>
       <c r="C128" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D128">
         <v>1</v>
       </c>
       <c r="E128">
-        <v>1.39</v>
+        <v>5.99</v>
       </c>
       <c r="F128">
-        <v>1.39</v>
+        <v>5.99</v>
       </c>
       <c r="G128" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -3284,19 +3293,19 @@
         <v>177</v>
       </c>
       <c r="C129" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D129">
         <v>1</v>
       </c>
       <c r="E129">
-        <v>6.77</v>
+        <v>1.39</v>
       </c>
       <c r="F129">
-        <v>6.77</v>
+        <v>1.39</v>
       </c>
       <c r="G129" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -3304,73 +3313,73 @@
         <v>176</v>
       </c>
       <c r="C130" t="s">
-        <v>101</v>
+        <v>336</v>
       </c>
       <c r="D130">
         <v>1</v>
       </c>
       <c r="E130">
-        <v>6.99</v>
+        <v>6.77</v>
       </c>
       <c r="F130">
-        <v>6.99</v>
+        <v>6.77</v>
       </c>
       <c r="G130" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
-        <v>103</v>
+        <v>175</v>
       </c>
       <c r="C131" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D131">
         <v>1</v>
       </c>
       <c r="E131">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
       <c r="F131">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
       <c r="G131" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
-        <v>254</v>
+        <v>103</v>
       </c>
       <c r="C132" t="s">
-        <v>255</v>
+        <v>104</v>
       </c>
       <c r="D132">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="E132">
+        <v>7.99</v>
+      </c>
+      <c r="F132">
+        <v>7.99</v>
       </c>
       <c r="G132" t="s">
-        <v>256</v>
+        <v>105</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
-        <v>175</v>
+        <v>253</v>
       </c>
       <c r="C133" t="s">
-        <v>106</v>
+        <v>254</v>
       </c>
       <c r="D133">
-        <v>1</v>
-      </c>
-      <c r="E133">
-        <v>7.98</v>
-      </c>
-      <c r="F133">
-        <v>7.98</v>
+        <v>3</v>
       </c>
       <c r="G133" t="s">
-        <v>107</v>
+        <v>255</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -3378,371 +3387,374 @@
         <v>174</v>
       </c>
       <c r="C134" t="s">
-        <v>338</v>
+        <v>106</v>
       </c>
       <c r="D134">
         <v>1</v>
       </c>
       <c r="E134">
+        <v>7.98</v>
+      </c>
+      <c r="F134">
+        <v>7.98</v>
+      </c>
+      <c r="G134" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B135" t="s">
+        <v>173</v>
+      </c>
+      <c r="C135" t="s">
+        <v>337</v>
+      </c>
+      <c r="D135">
+        <v>1</v>
+      </c>
+      <c r="E135">
         <v>29</v>
       </c>
-      <c r="F134">
+      <c r="F135">
         <v>29</v>
       </c>
-      <c r="G134" t="s">
+      <c r="G135" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
         <v>158</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B139" t="s">
-        <v>217</v>
-      </c>
-      <c r="C139" t="s">
-        <v>339</v>
-      </c>
-      <c r="D139">
-        <v>1</v>
-      </c>
-      <c r="E139">
-        <v>259.29000000000002</v>
-      </c>
-      <c r="F139">
-        <v>259.29000000000002</v>
-      </c>
-      <c r="G139" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C140" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D140">
         <v>1</v>
       </c>
       <c r="E140">
-        <v>94.71</v>
+        <v>259.29000000000002</v>
       </c>
       <c r="F140">
-        <v>94.71</v>
+        <v>259.29000000000002</v>
       </c>
       <c r="G140" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C141" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D141">
         <v>1</v>
       </c>
       <c r="E141">
-        <v>1975.8</v>
+        <v>94.71</v>
       </c>
       <c r="F141">
-        <v>1975.8</v>
+        <v>94.71</v>
       </c>
       <c r="G141" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C142" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D142">
         <v>1</v>
       </c>
       <c r="E142">
+        <v>1975.8</v>
+      </c>
+      <c r="F142">
+        <v>1975.8</v>
+      </c>
+      <c r="G142" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B143" t="s">
+        <v>219</v>
+      </c>
+      <c r="C143" t="s">
+        <v>341</v>
+      </c>
+      <c r="D143">
+        <v>1</v>
+      </c>
+      <c r="E143">
         <v>3247.41</v>
       </c>
-      <c r="F142">
+      <c r="F143">
         <v>3247.41</v>
       </c>
-      <c r="G142" t="s">
+      <c r="G143" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145" s="1" t="s">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
         <v>159</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B147" t="s">
-        <v>221</v>
-      </c>
-      <c r="C147" t="s">
-        <v>114</v>
-      </c>
-      <c r="D147">
-        <v>1</v>
-      </c>
-      <c r="E147">
-        <v>6.78</v>
-      </c>
-      <c r="F147">
-        <v>6.78</v>
-      </c>
-      <c r="G147" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C148" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D148">
         <v>1</v>
       </c>
       <c r="E148">
-        <v>43.99</v>
+        <v>6.78</v>
       </c>
       <c r="F148">
-        <v>43.99</v>
+        <v>6.78</v>
       </c>
       <c r="G148" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B149" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C149" t="s">
-        <v>164</v>
+        <v>116</v>
       </c>
       <c r="D149">
         <v>1</v>
       </c>
       <c r="E149">
-        <v>166.3</v>
+        <v>43.99</v>
       </c>
       <c r="F149">
-        <v>166.3</v>
-      </c>
-      <c r="G149" s="5" t="s">
-        <v>147</v>
+        <v>43.99</v>
+      </c>
+      <c r="G149" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C150" t="s">
-        <v>118</v>
+        <v>164</v>
       </c>
       <c r="D150">
         <v>1</v>
       </c>
       <c r="E150">
-        <v>4.95</v>
+        <v>166.3</v>
       </c>
       <c r="F150">
-        <v>4.95</v>
-      </c>
-      <c r="G150" t="s">
-        <v>119</v>
+        <v>166.3</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C151" t="s">
-        <v>343</v>
+        <v>118</v>
       </c>
       <c r="D151">
         <v>1</v>
       </c>
       <c r="E151">
-        <v>55.94</v>
+        <v>4.95</v>
       </c>
       <c r="F151">
-        <v>55.94</v>
+        <v>4.95</v>
       </c>
       <c r="G151" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C152" t="s">
-        <v>344</v>
-      </c>
-      <c r="D152" t="s">
-        <v>121</v>
+        <v>342</v>
+      </c>
+      <c r="D152">
+        <v>1</v>
       </c>
       <c r="E152">
-        <v>172</v>
+        <v>55.94</v>
       </c>
       <c r="F152">
-        <v>172</v>
+        <v>55.94</v>
       </c>
       <c r="G152" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C153" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D153" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E153">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="F153">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="G153" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C154" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D154" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E154">
-        <v>303</v>
+        <v>141</v>
       </c>
       <c r="F154">
-        <v>303</v>
+        <v>141</v>
       </c>
       <c r="G154" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B155" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C155" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D155" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E155">
-        <v>253</v>
+        <v>303</v>
       </c>
       <c r="F155">
-        <v>253</v>
+        <v>303</v>
       </c>
       <c r="G155" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B156" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C156" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D156" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E156">
-        <v>111</v>
+        <v>253</v>
       </c>
       <c r="F156">
-        <v>111</v>
+        <v>253</v>
       </c>
       <c r="G156" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B157" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C157" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D157" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E157">
-        <v>93.1</v>
+        <v>111</v>
       </c>
       <c r="F157">
-        <v>93.1</v>
+        <v>111</v>
       </c>
       <c r="G157" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C158" t="s">
-        <v>133</v>
-      </c>
-      <c r="D158">
-        <v>1</v>
+        <v>348</v>
+      </c>
+      <c r="D158" t="s">
+        <v>131</v>
       </c>
       <c r="E158">
-        <v>7.31</v>
+        <v>93.1</v>
       </c>
       <c r="F158">
-        <v>7.31</v>
+        <v>93.1</v>
       </c>
       <c r="G158" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C159" t="s">
-        <v>2</v>
-      </c>
-      <c r="D159" t="s">
-        <v>2</v>
-      </c>
-      <c r="F159" t="s">
-        <v>2</v>
+        <v>133</v>
+      </c>
+      <c r="D159">
+        <v>1</v>
+      </c>
+      <c r="E159">
+        <v>7.31</v>
+      </c>
+      <c r="F159">
+        <v>7.31</v>
       </c>
       <c r="G159" t="s">
-        <v>2</v>
+        <v>134</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C160" t="s">
         <v>2</v>
@@ -3754,6 +3766,23 @@
         <v>2</v>
       </c>
       <c r="G160" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B161" t="s">
+        <v>233</v>
+      </c>
+      <c r="C161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D161" t="s">
+        <v>2</v>
+      </c>
+      <c r="F161" t="s">
+        <v>2</v>
+      </c>
+      <c r="G161" t="s">
         <v>2</v>
       </c>
     </row>

--- a/Bill of Materials.xlsx
+++ b/Bill of Materials.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\groups\nordinrsrch\Kendon\OS1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71CFC8E6-25E5-4FE5-8F52-53F15F2726D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD9F94D-B153-4A34-89F9-249945BFEA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25320" yWindow="2235" windowWidth="25440" windowHeight="15270" xr2:uid="{18FE35BA-1422-49DD-9CBC-F02C04230EF8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{18FE35BA-1422-49DD-9CBC-F02C04230EF8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="360">
   <si>
     <t>Designator</t>
   </si>
@@ -247,9 +247,6 @@
   </si>
   <si>
     <t xml:space="preserve"> https://www.pololu.com/product/4733 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://www.pololu.com/product/3257 </t>
   </si>
   <si>
     <t xml:space="preserve"> https://www.servocity.com/2303-series-steel-mod-0.8-pinion-gear-4mm-round-bore-15-tooth-/ </t>
@@ -1009,9 +1006,6 @@
     <t xml:space="preserve"> MP6550 Single Brushed DC Motor Driver Carrier (Item #: 4733)</t>
   </si>
   <si>
-    <t xml:space="preserve"> 227:1 Metal Gearmotor 25Dx56L mm LP 12V (Item #: 3257)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 2303 Series Steel, MOD 0.8 Pinion Gear (4mm Round Bore, 15 Tooth) (Item #: 2303-0004-0015)</t>
   </si>
   <si>
@@ -1136,6 +1130,33 @@
   </si>
   <si>
     <t>https://a.co/d/08zMVh81</t>
+  </si>
+  <si>
+    <t>Safety</t>
+  </si>
+  <si>
+    <t>UV safety goggles</t>
+  </si>
+  <si>
+    <t>LG6, Laser Safety Glasses, Clear Lenses, 93% Visible Light Transmission, Universal Style</t>
+  </si>
+  <si>
+    <t>https://www.thorlabs.com/item/LG6</t>
+  </si>
+  <si>
+    <t>https://www.mcmaster.com/5415K17/</t>
+  </si>
+  <si>
+    <t>Worm-Drive Clamps for Firm Hose and Tube, Steel Screw, 1/2" Band Width, 1-1/16" to 2" Clamp ID (Item #: 5415K17)</t>
+  </si>
+  <si>
+    <t>Hose Clamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 227:1 Metal Gearmotor 25Dx56L mm MP 12V (Item #: 3233)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://www.pololu.com/product/3233</t>
   </si>
 </sst>
 </file>
@@ -1513,7 +1534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A189396B-8023-47A8-ACB7-2D166A986A96}">
-  <dimension ref="A1:K161"/>
+  <dimension ref="A1:K163"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" customWidth="1"/>
@@ -1527,29 +1548,29 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="H1" s="1"/>
       <c r="K1" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -1563,11 +1584,11 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -1575,8 +1596,8 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="K3">
-        <f>SUM(F5:F159)</f>
-        <v>69563.510000000009</v>
+        <f>SUM(F5:F163)</f>
+        <v>69766.73</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1590,10 +1611,10 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -1610,10 +1631,10 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -1630,10 +1651,10 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1650,10 +1671,10 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1670,36 +1691,36 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
+        <v>255</v>
+      </c>
+      <c r="C9" t="s">
+        <v>264</v>
+      </c>
+      <c r="D9" t="s">
+        <v>258</v>
+      </c>
+      <c r="E9" t="s">
+        <v>138</v>
+      </c>
+      <c r="G9" t="s">
         <v>256</v>
-      </c>
-      <c r="C9" t="s">
-        <v>265</v>
-      </c>
-      <c r="D9" t="s">
-        <v>259</v>
-      </c>
-      <c r="E9" t="s">
-        <v>139</v>
-      </c>
-      <c r="G9" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1707,13 +1728,13 @@
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D11" t="s">
         <v>8</v>
       </c>
       <c r="E11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F11">
         <v>500</v>
@@ -1724,21 +1745,21 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
+        <v>261</v>
+      </c>
+      <c r="C12" t="s">
         <v>262</v>
       </c>
-      <c r="C12" t="s">
-        <v>263</v>
-      </c>
       <c r="D12" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -1758,10 +1779,10 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C14" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -1778,10 +1799,10 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1796,29 +1817,29 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>245</v>
-      </c>
-      <c r="C19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <v>6.96</v>
-      </c>
-      <c r="F19">
-        <v>6.96</v>
-      </c>
-      <c r="G19" t="s">
-        <v>15</v>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>357</v>
+      </c>
+      <c r="C16" t="s">
+        <v>356</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>12.63</v>
+      </c>
+      <c r="F16">
+        <v>12.63</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1826,119 +1847,119 @@
         <v>244</v>
       </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>14.99</v>
+        <v>6.96</v>
       </c>
       <c r="F20">
-        <v>14.99</v>
+        <v>6.96</v>
       </c>
       <c r="G20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>141</v>
+        <v>243</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E21">
-        <v>7.99</v>
+        <v>14.99</v>
       </c>
       <c r="F21">
-        <v>7.99</v>
+        <v>14.99</v>
       </c>
       <c r="G21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>349</v>
+        <v>140</v>
       </c>
       <c r="C22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>7.99</v>
+      </c>
+      <c r="F22">
+        <v>7.99</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>347</v>
+      </c>
+      <c r="C23" t="s">
+        <v>273</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23">
+        <v>0.1</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="D22">
-        <v>3</v>
-      </c>
-      <c r="E22">
-        <v>0.1</v>
-      </c>
-      <c r="F22">
-        <v>3</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
+      <c r="D24" s="2">
+        <v>6</v>
+      </c>
+      <c r="E24">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F24">
+        <v>0.84</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D23" s="2">
-        <v>6</v>
-      </c>
-      <c r="E23">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="F23">
-        <v>0.84</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>145</v>
-      </c>
-      <c r="C24" t="s">
-        <v>276</v>
-      </c>
-      <c r="D24">
-        <v>3</v>
-      </c>
-      <c r="E24">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="F24">
-        <v>1.65</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>243</v>
+        <v>144</v>
       </c>
       <c r="C25" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25">
-        <v>175</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="F25">
-        <v>175</v>
+        <v>1.65</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1946,19 +1967,19 @@
         <v>242</v>
       </c>
       <c r="C26" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26">
-        <v>5</v>
+        <v>175</v>
       </c>
       <c r="F26">
-        <v>5</v>
-      </c>
-      <c r="G26" t="s">
-        <v>20</v>
+        <v>175</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1966,19 +1987,19 @@
         <v>241</v>
       </c>
       <c r="C27" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27">
-        <v>19.95</v>
+        <v>5</v>
       </c>
       <c r="F27">
-        <v>19.95</v>
+        <v>5</v>
       </c>
       <c r="G27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1986,19 +2007,19 @@
         <v>240</v>
       </c>
       <c r="C28" t="s">
-        <v>22</v>
+        <v>278</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28">
-        <v>164.99</v>
+        <v>19.95</v>
       </c>
       <c r="F28">
-        <v>164.99</v>
+        <v>19.95</v>
       </c>
       <c r="G28" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2006,19 +2027,19 @@
         <v>239</v>
       </c>
       <c r="C29" t="s">
-        <v>280</v>
+        <v>22</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29">
-        <v>14.04</v>
+        <v>164.99</v>
       </c>
       <c r="F29">
-        <v>14.04</v>
+        <v>164.99</v>
       </c>
       <c r="G29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2026,19 +2047,19 @@
         <v>238</v>
       </c>
       <c r="C30" t="s">
-        <v>25</v>
+        <v>279</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>30.05</v>
+        <v>14.04</v>
       </c>
       <c r="F30">
-        <v>60.1</v>
+        <v>14.04</v>
       </c>
       <c r="G30" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2046,84 +2067,84 @@
         <v>237</v>
       </c>
       <c r="C31" t="s">
-        <v>271</v>
+        <v>25</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31">
-        <v>80.099999999999994</v>
+        <v>30.05</v>
       </c>
       <c r="F31">
-        <v>80.099999999999994</v>
+        <v>60.1</v>
       </c>
       <c r="G31" t="s">
-        <v>109</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
+        <v>236</v>
+      </c>
+      <c r="C32" t="s">
+        <v>270</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>80.099999999999994</v>
+      </c>
+      <c r="F32">
+        <v>80.099999999999994</v>
+      </c>
+      <c r="G32" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>348</v>
+      </c>
+      <c r="C33" t="s">
+        <v>349</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>5.99</v>
+      </c>
+      <c r="F33">
+        <v>5.99</v>
+      </c>
+      <c r="G33" t="s">
         <v>350</v>
       </c>
-      <c r="C32" t="s">
-        <v>351</v>
-      </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-      <c r="E32">
-        <v>5.99</v>
-      </c>
-      <c r="F32">
-        <v>5.99</v>
-      </c>
-      <c r="G32" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" t="s">
-        <v>28</v>
-      </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="E36">
-        <v>47.22</v>
-      </c>
-      <c r="F36">
-        <v>47.22</v>
-      </c>
-      <c r="G36" t="s">
-        <v>29</v>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>236</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D37">
         <v>1</v>
       </c>
       <c r="E37">
-        <v>16.899999999999999</v>
+        <v>47.22</v>
       </c>
       <c r="F37">
-        <v>16.899999999999999</v>
+        <v>47.22</v>
       </c>
       <c r="G37" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2131,19 +2152,19 @@
         <v>235</v>
       </c>
       <c r="C38" t="s">
-        <v>281</v>
+        <v>30</v>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E38">
-        <v>3.35</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="F38">
-        <v>16.77</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="G38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2151,84 +2172,124 @@
         <v>234</v>
       </c>
       <c r="C39" t="s">
+        <v>280</v>
+      </c>
+      <c r="D39">
+        <v>5</v>
+      </c>
+      <c r="E39">
+        <v>3.35</v>
+      </c>
+      <c r="F39">
+        <v>16.77</v>
+      </c>
+      <c r="G39" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C40" t="s">
+        <v>281</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="E40">
+        <v>7.6</v>
+      </c>
+      <c r="F40">
+        <v>15.2</v>
+      </c>
+      <c r="G40" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" t="s">
         <v>282</v>
       </c>
-      <c r="D39">
-        <v>2</v>
-      </c>
-      <c r="E39">
-        <v>7.6</v>
-      </c>
-      <c r="F39">
-        <v>15.2</v>
-      </c>
-      <c r="G39" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>149</v>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>6.38</v>
+      </c>
+      <c r="F44">
+        <v>6.38</v>
+      </c>
+      <c r="G44" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C45" t="s">
         <v>283</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E45">
-        <v>6.38</v>
+        <v>12.46</v>
       </c>
       <c r="F45">
-        <v>6.38</v>
+        <v>49.9</v>
       </c>
       <c r="G45" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C46" t="s">
-        <v>284</v>
+        <v>36</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E46">
-        <v>12.46</v>
+        <v>8.7899999999999991</v>
       </c>
       <c r="F46">
-        <v>49.9</v>
+        <v>26.37</v>
       </c>
       <c r="G46" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C47" t="s">
-        <v>36</v>
+        <v>284</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E47">
-        <v>8.7899999999999991</v>
+        <v>97.5</v>
       </c>
       <c r="F47">
-        <v>26.37</v>
+        <v>97.5</v>
       </c>
       <c r="G47" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -2239,16 +2300,16 @@
         <v>285</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48">
-        <v>97.5</v>
+        <v>15.2</v>
       </c>
       <c r="F48">
-        <v>97.5</v>
+        <v>30.4</v>
       </c>
       <c r="G48" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -2256,44 +2317,44 @@
         <v>183</v>
       </c>
       <c r="C49" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>15.2</v>
+        <v>6.44</v>
       </c>
       <c r="F49">
-        <v>30.4</v>
+        <v>6.44</v>
       </c>
       <c r="G49" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>184</v>
+        <v>41</v>
       </c>
       <c r="C50" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="D50">
         <v>1</v>
       </c>
       <c r="E50">
-        <v>6.44</v>
+        <v>137.97999999999999</v>
       </c>
       <c r="F50">
-        <v>6.44</v>
+        <v>137.97999999999999</v>
       </c>
       <c r="G50" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>41</v>
+        <v>184</v>
       </c>
       <c r="C51" t="s">
         <v>287</v>
@@ -2302,13 +2363,13 @@
         <v>1</v>
       </c>
       <c r="E51">
-        <v>137.97999999999999</v>
+        <v>8.98</v>
       </c>
       <c r="F51">
-        <v>137.97999999999999</v>
+        <v>8.98</v>
       </c>
       <c r="G51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -2316,184 +2377,184 @@
         <v>185</v>
       </c>
       <c r="C52" t="s">
+        <v>44</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52">
+        <v>10.55</v>
+      </c>
+      <c r="F52">
+        <v>10.55</v>
+      </c>
+      <c r="G52" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>46</v>
+      </c>
+      <c r="C56" t="s">
         <v>288</v>
       </c>
-      <c r="D52">
-        <v>1</v>
-      </c>
-      <c r="E52">
-        <v>8.98</v>
-      </c>
-      <c r="F52">
-        <v>8.98</v>
-      </c>
-      <c r="G52" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B53" t="s">
-        <v>186</v>
-      </c>
-      <c r="C53" t="s">
-        <v>44</v>
-      </c>
-      <c r="D53">
-        <v>1</v>
-      </c>
-      <c r="E53">
-        <v>10.55</v>
-      </c>
-      <c r="F53">
-        <v>10.55</v>
-      </c>
-      <c r="G53" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>150</v>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56" s="4">
+        <v>9.33</v>
+      </c>
+      <c r="F56">
+        <v>9.33</v>
+      </c>
+      <c r="G56" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>46</v>
+        <v>171</v>
       </c>
       <c r="C57" t="s">
         <v>289</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="4">
         <v>1</v>
       </c>
       <c r="E57" s="4">
-        <v>9.33</v>
+        <v>8.07</v>
       </c>
       <c r="F57">
-        <v>9.33</v>
+        <v>8.07</v>
       </c>
       <c r="G57" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="C58" t="s">
         <v>290</v>
       </c>
-      <c r="D58" s="4">
+      <c r="D58">
         <v>1</v>
       </c>
       <c r="E58" s="4">
-        <v>8.07</v>
+        <v>10.28</v>
       </c>
       <c r="F58">
-        <v>8.07</v>
+        <v>10.28</v>
       </c>
       <c r="G58" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="C59" t="s">
         <v>291</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="4">
         <v>1</v>
       </c>
       <c r="E59" s="4">
-        <v>10.28</v>
+        <v>12.71</v>
       </c>
       <c r="F59">
-        <v>10.28</v>
+        <v>12.71</v>
       </c>
       <c r="G59" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>50</v>
+        <v>190</v>
       </c>
       <c r="C60" t="s">
         <v>292</v>
       </c>
-      <c r="D60" s="4">
-        <v>1</v>
+      <c r="D60">
+        <v>4</v>
       </c>
       <c r="E60" s="4">
-        <v>12.71</v>
+        <v>8.6300000000000008</v>
       </c>
       <c r="F60">
-        <v>12.71</v>
+        <v>34.520000000000003</v>
       </c>
       <c r="G60" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="C61" t="s">
         <v>293</v>
       </c>
       <c r="D61">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E61" s="4">
-        <v>8.6300000000000008</v>
+        <v>10.3</v>
       </c>
       <c r="F61">
-        <v>34.520000000000003</v>
+        <v>10.3</v>
       </c>
       <c r="G61" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C62" t="s">
         <v>294</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="4">
-        <v>10.3</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="F62">
-        <v>10.3</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="G62" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>55</v>
+        <v>191</v>
       </c>
       <c r="C63" t="s">
         <v>295</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" s="4">
-        <v>8.0299999999999994</v>
+        <v>13.16</v>
       </c>
       <c r="F63">
-        <v>16.059999999999999</v>
-      </c>
-      <c r="G63" t="s">
-        <v>56</v>
+        <v>13.16</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -2501,109 +2562,109 @@
         <v>192</v>
       </c>
       <c r="C64" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D64">
         <v>1</v>
       </c>
       <c r="E64" s="4">
-        <v>13.16</v>
+        <v>19.3</v>
       </c>
       <c r="F64">
-        <v>13.16</v>
-      </c>
-      <c r="G64" s="5" t="s">
-        <v>297</v>
+        <v>19.3</v>
+      </c>
+      <c r="G64" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>193</v>
+        <v>58</v>
       </c>
       <c r="C65" t="s">
         <v>300</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" s="4">
-        <v>19.3</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="F65">
-        <v>19.3</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="G65" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C66" t="s">
         <v>301</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" s="4">
-        <v>8.0299999999999994</v>
+        <v>10.3</v>
       </c>
       <c r="F66">
-        <v>16.059999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="G66" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C67" t="s">
+        <v>165</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67" s="4">
+        <v>6.49</v>
+      </c>
+      <c r="F67">
+        <v>6.49</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>62</v>
+      </c>
+      <c r="C71" t="s">
         <v>302</v>
       </c>
-      <c r="D67">
-        <v>1</v>
-      </c>
-      <c r="E67" s="4">
-        <v>10.3</v>
-      </c>
-      <c r="F67">
-        <v>10.3</v>
-      </c>
-      <c r="G67" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B68" t="s">
-        <v>61</v>
-      </c>
-      <c r="C68" t="s">
-        <v>166</v>
-      </c>
-      <c r="D68">
-        <v>1</v>
-      </c>
-      <c r="E68" s="4">
-        <v>6.49</v>
-      </c>
-      <c r="F68">
-        <v>6.49</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>151</v>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71">
+        <v>3392.5</v>
+      </c>
+      <c r="F71">
+        <v>3392.5</v>
+      </c>
+      <c r="G71" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C72" t="s">
         <v>303</v>
@@ -2612,18 +2673,18 @@
         <v>1</v>
       </c>
       <c r="E72">
-        <v>3392.5</v>
+        <v>3847.57</v>
       </c>
       <c r="F72">
-        <v>3392.5</v>
+        <v>3847.57</v>
       </c>
       <c r="G72" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>64</v>
+        <v>168</v>
       </c>
       <c r="C73" t="s">
         <v>304</v>
@@ -2632,38 +2693,38 @@
         <v>1</v>
       </c>
       <c r="E73">
-        <v>3847.57</v>
+        <v>1177.03</v>
       </c>
       <c r="F73">
-        <v>3847.57</v>
+        <v>1177.03</v>
       </c>
       <c r="G73" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>169</v>
+        <v>67</v>
       </c>
       <c r="C74" t="s">
+        <v>306</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="E74">
+        <v>6500</v>
+      </c>
+      <c r="F74">
+        <v>6500</v>
+      </c>
+      <c r="G74" s="5" t="s">
         <v>305</v>
-      </c>
-      <c r="D74">
-        <v>1</v>
-      </c>
-      <c r="E74">
-        <v>1177.03</v>
-      </c>
-      <c r="F74">
-        <v>1177.03</v>
-      </c>
-      <c r="G74" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>67</v>
+        <v>193</v>
       </c>
       <c r="C75" t="s">
         <v>307</v>
@@ -2672,38 +2733,38 @@
         <v>1</v>
       </c>
       <c r="E75">
-        <v>6500</v>
+        <v>89.61</v>
       </c>
       <c r="F75">
-        <v>6500</v>
-      </c>
-      <c r="G75" s="5" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B76" t="s">
+        <v>89.61</v>
+      </c>
+      <c r="G75" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
         <v>194</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C80" t="s">
         <v>308</v>
       </c>
-      <c r="D76">
-        <v>1</v>
-      </c>
-      <c r="E76">
-        <v>89.61</v>
-      </c>
-      <c r="F76">
-        <v>89.61</v>
-      </c>
-      <c r="G76" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>152</v>
+      <c r="D80">
+        <v>1</v>
+      </c>
+      <c r="E80">
+        <v>5.95</v>
+      </c>
+      <c r="F80">
+        <v>5.95</v>
+      </c>
+      <c r="G80" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -2711,19 +2772,19 @@
         <v>195</v>
       </c>
       <c r="C81" t="s">
-        <v>309</v>
+        <v>358</v>
       </c>
       <c r="D81">
         <v>1</v>
       </c>
       <c r="E81">
-        <v>5.95</v>
+        <v>33.950000000000003</v>
       </c>
       <c r="F81">
-        <v>5.95</v>
+        <v>33.950000000000003</v>
       </c>
       <c r="G81" t="s">
-        <v>69</v>
+        <v>359</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -2731,16 +2792,16 @@
         <v>196</v>
       </c>
       <c r="C82" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82">
-        <v>33.950000000000003</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="F82">
-        <v>33.950000000000003</v>
+        <v>19.89</v>
       </c>
       <c r="G82" t="s">
         <v>70</v>
@@ -2751,49 +2812,49 @@
         <v>197</v>
       </c>
       <c r="C83" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83">
-        <v>9.9499999999999993</v>
+        <v>10.95</v>
       </c>
       <c r="F83">
-        <v>19.89</v>
+        <v>10.95</v>
       </c>
       <c r="G83" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B84" t="s">
-        <v>198</v>
-      </c>
-      <c r="C84" t="s">
-        <v>312</v>
-      </c>
-      <c r="D84">
-        <v>1</v>
-      </c>
-      <c r="E84">
-        <v>10.95</v>
-      </c>
-      <c r="F84">
-        <v>10.95</v>
-      </c>
-      <c r="G84" t="s">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>170</v>
+      </c>
+      <c r="C88" t="s">
+        <v>311</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+      <c r="E88">
+        <v>86</v>
+      </c>
+      <c r="F88">
+        <v>86</v>
+      </c>
+      <c r="G88" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C89" t="s">
         <v>313</v>
@@ -2802,58 +2863,58 @@
         <v>1</v>
       </c>
       <c r="E89">
-        <v>86</v>
+        <v>715</v>
       </c>
       <c r="F89">
-        <v>86</v>
-      </c>
-      <c r="G89" t="s">
-        <v>73</v>
+        <v>715</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="C90" t="s">
+        <v>314</v>
+      </c>
+      <c r="D90">
+        <v>1</v>
+      </c>
+      <c r="E90">
+        <v>120</v>
+      </c>
+      <c r="F90">
+        <v>120</v>
+      </c>
+      <c r="G90" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="D90">
-        <v>1</v>
-      </c>
-      <c r="E90">
-        <v>715</v>
-      </c>
-      <c r="F90">
-        <v>715</v>
-      </c>
-      <c r="G90" s="5" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B91" t="s">
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B96" t="s">
+        <v>198</v>
+      </c>
+      <c r="C96" t="s">
+        <v>316</v>
+      </c>
+      <c r="D96">
+        <v>2</v>
+      </c>
+      <c r="E96">
+        <v>938.6</v>
+      </c>
+      <c r="F96">
+        <v>1877.2</v>
+      </c>
+      <c r="G96" t="s">
         <v>74</v>
-      </c>
-      <c r="C91" t="s">
-        <v>316</v>
-      </c>
-      <c r="D91">
-        <v>1</v>
-      </c>
-      <c r="E91">
-        <v>120</v>
-      </c>
-      <c r="F91">
-        <v>120</v>
-      </c>
-      <c r="G91" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -2861,16 +2922,16 @@
         <v>199</v>
       </c>
       <c r="C97" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97">
-        <v>938.6</v>
+        <v>122.03</v>
       </c>
       <c r="F97">
-        <v>1877.2</v>
+        <v>122.03</v>
       </c>
       <c r="G97" t="s">
         <v>75</v>
@@ -2881,16 +2942,16 @@
         <v>200</v>
       </c>
       <c r="C98" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E98">
-        <v>122.03</v>
+        <v>826.75</v>
       </c>
       <c r="F98">
-        <v>122.03</v>
+        <v>2480.25</v>
       </c>
       <c r="G98" t="s">
         <v>76</v>
@@ -2901,16 +2962,16 @@
         <v>201</v>
       </c>
       <c r="C99" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E99">
-        <v>826.75</v>
+        <v>662.5</v>
       </c>
       <c r="F99">
-        <v>2480.25</v>
+        <v>662.5</v>
       </c>
       <c r="G99" t="s">
         <v>77</v>
@@ -2921,16 +2982,16 @@
         <v>202</v>
       </c>
       <c r="C100" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D100">
         <v>1</v>
       </c>
       <c r="E100">
-        <v>662.5</v>
+        <v>360.4</v>
       </c>
       <c r="F100">
-        <v>662.5</v>
+        <v>360.4</v>
       </c>
       <c r="G100" t="s">
         <v>78</v>
@@ -2941,16 +3002,16 @@
         <v>203</v>
       </c>
       <c r="C101" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D101">
         <v>1</v>
       </c>
       <c r="E101">
-        <v>360.4</v>
+        <v>2100</v>
       </c>
       <c r="F101">
-        <v>360.4</v>
+        <v>2100</v>
       </c>
       <c r="G101" t="s">
         <v>79</v>
@@ -2961,16 +3022,16 @@
         <v>204</v>
       </c>
       <c r="C102" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D102">
         <v>1</v>
       </c>
       <c r="E102">
-        <v>2100</v>
+        <v>4800</v>
       </c>
       <c r="F102">
-        <v>2100</v>
+        <v>4800</v>
       </c>
       <c r="G102" t="s">
         <v>80</v>
@@ -2987,13 +3048,16 @@
         <v>1</v>
       </c>
       <c r="E103">
-        <v>4800</v>
+        <v>4300</v>
       </c>
       <c r="F103">
-        <v>4800</v>
+        <v>4300</v>
       </c>
       <c r="G103" t="s">
         <v>81</v>
+      </c>
+      <c r="H103" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -3001,21 +3065,18 @@
         <v>206</v>
       </c>
       <c r="C104" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D104">
         <v>1</v>
       </c>
       <c r="E104">
-        <v>4300</v>
+        <v>320</v>
       </c>
       <c r="F104">
-        <v>4300</v>
+        <v>320</v>
       </c>
       <c r="G104" t="s">
-        <v>82</v>
-      </c>
-      <c r="H104" t="s">
         <v>83</v>
       </c>
     </row>
@@ -3024,44 +3085,44 @@
         <v>207</v>
       </c>
       <c r="C105" t="s">
+        <v>84</v>
+      </c>
+      <c r="D105">
+        <v>1</v>
+      </c>
+      <c r="E105">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="F105">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="G105" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B110" t="s">
+        <v>208</v>
+      </c>
+      <c r="C110" t="s">
         <v>325</v>
       </c>
-      <c r="D105">
-        <v>1</v>
-      </c>
-      <c r="E105">
-        <v>320</v>
-      </c>
-      <c r="F105">
-        <v>320</v>
-      </c>
-      <c r="G105" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B106" t="s">
-        <v>208</v>
-      </c>
-      <c r="C106" t="s">
-        <v>85</v>
-      </c>
-      <c r="D106">
-        <v>1</v>
-      </c>
-      <c r="E106">
-        <v>8.2899999999999991</v>
-      </c>
-      <c r="F106">
-        <v>8.2899999999999991</v>
-      </c>
-      <c r="G106" t="s">
+      <c r="D110">
+        <v>1</v>
+      </c>
+      <c r="E110">
+        <v>381.34</v>
+      </c>
+      <c r="F110">
+        <v>381.34</v>
+      </c>
+      <c r="G110" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -3069,16 +3130,16 @@
         <v>209</v>
       </c>
       <c r="C111" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D111">
         <v>1</v>
       </c>
       <c r="E111">
-        <v>381.34</v>
+        <v>532.59</v>
       </c>
       <c r="F111">
-        <v>381.34</v>
+        <v>532.59</v>
       </c>
       <c r="G111" t="s">
         <v>87</v>
@@ -3089,16 +3150,16 @@
         <v>210</v>
       </c>
       <c r="C112" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D112">
         <v>1</v>
       </c>
       <c r="E112">
-        <v>532.59</v>
+        <v>474.23</v>
       </c>
       <c r="F112">
-        <v>532.59</v>
+        <v>474.23</v>
       </c>
       <c r="G112" t="s">
         <v>88</v>
@@ -3109,47 +3170,44 @@
         <v>211</v>
       </c>
       <c r="C113" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D113">
         <v>1</v>
       </c>
       <c r="E113">
-        <v>474.23</v>
+        <v>5.99</v>
       </c>
       <c r="F113">
-        <v>474.23</v>
+        <v>5.99</v>
       </c>
       <c r="G113" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B114" t="s">
+      <c r="H113" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B118" t="s">
         <v>212</v>
       </c>
-      <c r="C114" t="s">
-        <v>330</v>
-      </c>
-      <c r="D114">
-        <v>1</v>
-      </c>
-      <c r="E114">
-        <v>5.99</v>
-      </c>
-      <c r="F114">
-        <v>5.99</v>
-      </c>
-      <c r="G114" t="s">
+      <c r="C118" t="s">
         <v>90</v>
       </c>
-      <c r="H114" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
-        <v>156</v>
+      <c r="D118">
+        <v>1</v>
+      </c>
+      <c r="F118">
+        <v>20000</v>
+      </c>
+      <c r="G118" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -3157,16 +3215,16 @@
         <v>213</v>
       </c>
       <c r="C119" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D119">
         <v>1</v>
       </c>
       <c r="F119">
-        <v>20000</v>
-      </c>
-      <c r="G119" t="s">
-        <v>92</v>
+        <v>5000</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -3174,55 +3232,58 @@
         <v>214</v>
       </c>
       <c r="C120" t="s">
+        <v>162</v>
+      </c>
+      <c r="D120">
+        <v>1</v>
+      </c>
+      <c r="F120">
+        <v>800</v>
+      </c>
+      <c r="G120" t="s">
         <v>93</v>
       </c>
-      <c r="D120">
-        <v>1</v>
-      </c>
-      <c r="F120">
-        <v>5000</v>
-      </c>
-      <c r="G120" s="5" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B121" t="s">
-        <v>215</v>
-      </c>
-      <c r="C121" t="s">
-        <v>163</v>
-      </c>
-      <c r="D121">
-        <v>1</v>
-      </c>
-      <c r="F121">
-        <v>800</v>
-      </c>
-      <c r="G121" t="s">
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B124" t="s">
+        <v>180</v>
+      </c>
+      <c r="C124" t="s">
+        <v>329</v>
+      </c>
+      <c r="D124">
+        <v>1</v>
+      </c>
+      <c r="E124">
+        <v>97.63</v>
+      </c>
+      <c r="F124">
+        <v>97.63</v>
+      </c>
+      <c r="G124" t="s">
         <v>94</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="1" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C125" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D125">
         <v>1</v>
       </c>
       <c r="E125">
-        <v>97.63</v>
+        <v>0.94</v>
       </c>
       <c r="F125">
-        <v>97.63</v>
+        <v>0.94</v>
       </c>
       <c r="G125" t="s">
         <v>95</v>
@@ -3230,19 +3291,19 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C126" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D126">
         <v>1</v>
       </c>
       <c r="E126">
-        <v>0.94</v>
+        <v>2.52</v>
       </c>
       <c r="F126">
-        <v>0.94</v>
+        <v>2.52</v>
       </c>
       <c r="G126" t="s">
         <v>96</v>
@@ -3250,19 +3311,19 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C127" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D127">
         <v>1</v>
       </c>
       <c r="E127">
-        <v>2.52</v>
+        <v>5.99</v>
       </c>
       <c r="F127">
-        <v>2.52</v>
+        <v>5.99</v>
       </c>
       <c r="G127" t="s">
         <v>97</v>
@@ -3270,19 +3331,19 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C128" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D128">
         <v>1</v>
       </c>
       <c r="E128">
-        <v>5.99</v>
+        <v>1.39</v>
       </c>
       <c r="F128">
-        <v>5.99</v>
+        <v>1.39</v>
       </c>
       <c r="G128" t="s">
         <v>98</v>
@@ -3290,19 +3351,19 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C129" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D129">
         <v>1</v>
       </c>
       <c r="E129">
-        <v>1.39</v>
+        <v>6.77</v>
       </c>
       <c r="F129">
-        <v>1.39</v>
+        <v>6.77</v>
       </c>
       <c r="G129" t="s">
         <v>99</v>
@@ -3310,121 +3371,121 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C130" t="s">
-        <v>336</v>
+        <v>100</v>
       </c>
       <c r="D130">
         <v>1</v>
       </c>
       <c r="E130">
-        <v>6.77</v>
+        <v>6.99</v>
       </c>
       <c r="F130">
-        <v>6.77</v>
+        <v>6.99</v>
       </c>
       <c r="G130" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="C131" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D131">
         <v>1</v>
       </c>
       <c r="E131">
-        <v>6.99</v>
+        <v>7.99</v>
       </c>
       <c r="F131">
-        <v>6.99</v>
+        <v>7.99</v>
       </c>
       <c r="G131" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
-        <v>103</v>
+        <v>252</v>
       </c>
       <c r="C132" t="s">
-        <v>104</v>
+        <v>253</v>
       </c>
       <c r="D132">
-        <v>1</v>
-      </c>
-      <c r="E132">
-        <v>7.99</v>
-      </c>
-      <c r="F132">
-        <v>7.99</v>
+        <v>3</v>
       </c>
       <c r="G132" t="s">
-        <v>105</v>
+        <v>254</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
-        <v>253</v>
+        <v>173</v>
       </c>
       <c r="C133" t="s">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="D133">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="E133">
+        <v>7.98</v>
+      </c>
+      <c r="F133">
+        <v>7.98</v>
       </c>
       <c r="G133" t="s">
-        <v>255</v>
+        <v>106</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C134" t="s">
-        <v>106</v>
+        <v>335</v>
       </c>
       <c r="D134">
         <v>1</v>
       </c>
       <c r="E134">
-        <v>7.98</v>
+        <v>29</v>
       </c>
       <c r="F134">
-        <v>7.98</v>
+        <v>29</v>
       </c>
       <c r="G134" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B135" t="s">
-        <v>173</v>
-      </c>
-      <c r="C135" t="s">
-        <v>337</v>
-      </c>
-      <c r="D135">
-        <v>1</v>
-      </c>
-      <c r="E135">
-        <v>29</v>
-      </c>
-      <c r="F135">
-        <v>29</v>
-      </c>
-      <c r="G135" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="1" t="s">
-        <v>158</v>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B139" t="s">
+        <v>215</v>
+      </c>
+      <c r="C139" t="s">
+        <v>336</v>
+      </c>
+      <c r="D139">
+        <v>1</v>
+      </c>
+      <c r="E139">
+        <v>259.29000000000002</v>
+      </c>
+      <c r="F139">
+        <v>259.29000000000002</v>
+      </c>
+      <c r="G139" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -3432,16 +3493,16 @@
         <v>216</v>
       </c>
       <c r="C140" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D140">
         <v>1</v>
       </c>
       <c r="E140">
-        <v>259.29000000000002</v>
+        <v>94.71</v>
       </c>
       <c r="F140">
-        <v>259.29000000000002</v>
+        <v>94.71</v>
       </c>
       <c r="G140" t="s">
         <v>110</v>
@@ -3452,16 +3513,16 @@
         <v>217</v>
       </c>
       <c r="C141" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D141">
         <v>1</v>
       </c>
       <c r="E141">
-        <v>94.71</v>
+        <v>1975.8</v>
       </c>
       <c r="F141">
-        <v>94.71</v>
+        <v>1975.8</v>
       </c>
       <c r="G141" t="s">
         <v>111</v>
@@ -3472,44 +3533,44 @@
         <v>218</v>
       </c>
       <c r="C142" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D142">
         <v>1</v>
       </c>
       <c r="E142">
-        <v>1975.8</v>
+        <v>3247.41</v>
       </c>
       <c r="F142">
-        <v>1975.8</v>
+        <v>3247.41</v>
       </c>
       <c r="G142" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B143" t="s">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B147" t="s">
         <v>219</v>
       </c>
-      <c r="C143" t="s">
-        <v>341</v>
-      </c>
-      <c r="D143">
-        <v>1</v>
-      </c>
-      <c r="E143">
-        <v>3247.41</v>
-      </c>
-      <c r="F143">
-        <v>3247.41</v>
-      </c>
-      <c r="G143" t="s">
+      <c r="C147" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A146" s="1" t="s">
-        <v>159</v>
+      <c r="D147">
+        <v>1</v>
+      </c>
+      <c r="E147">
+        <v>6.78</v>
+      </c>
+      <c r="F147">
+        <v>6.78</v>
+      </c>
+      <c r="G147" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -3517,19 +3578,19 @@
         <v>220</v>
       </c>
       <c r="C148" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D148">
         <v>1</v>
       </c>
       <c r="E148">
-        <v>6.78</v>
+        <v>43.99</v>
       </c>
       <c r="F148">
-        <v>6.78</v>
+        <v>43.99</v>
       </c>
       <c r="G148" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -3537,19 +3598,19 @@
         <v>221</v>
       </c>
       <c r="C149" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="D149">
         <v>1</v>
       </c>
       <c r="E149">
-        <v>43.99</v>
+        <v>166.3</v>
       </c>
       <c r="F149">
-        <v>43.99</v>
-      </c>
-      <c r="G149" t="s">
-        <v>117</v>
+        <v>166.3</v>
+      </c>
+      <c r="G149" s="5" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -3557,19 +3618,19 @@
         <v>222</v>
       </c>
       <c r="C150" t="s">
-        <v>164</v>
+        <v>117</v>
       </c>
       <c r="D150">
         <v>1</v>
       </c>
       <c r="E150">
-        <v>166.3</v>
+        <v>4.95</v>
       </c>
       <c r="F150">
-        <v>166.3</v>
-      </c>
-      <c r="G150" s="5" t="s">
-        <v>147</v>
+        <v>4.95</v>
+      </c>
+      <c r="G150" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -3577,16 +3638,16 @@
         <v>223</v>
       </c>
       <c r="C151" t="s">
-        <v>118</v>
+        <v>340</v>
       </c>
       <c r="D151">
         <v>1</v>
       </c>
       <c r="E151">
-        <v>4.95</v>
+        <v>55.94</v>
       </c>
       <c r="F151">
-        <v>4.95</v>
+        <v>55.94</v>
       </c>
       <c r="G151" t="s">
         <v>119</v>
@@ -3597,19 +3658,19 @@
         <v>224</v>
       </c>
       <c r="C152" t="s">
-        <v>342</v>
-      </c>
-      <c r="D152">
-        <v>1</v>
+        <v>341</v>
+      </c>
+      <c r="D152" t="s">
+        <v>120</v>
       </c>
       <c r="E152">
-        <v>55.94</v>
+        <v>172</v>
       </c>
       <c r="F152">
-        <v>55.94</v>
+        <v>172</v>
       </c>
       <c r="G152" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -3617,19 +3678,19 @@
         <v>225</v>
       </c>
       <c r="C153" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D153" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E153">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="F153">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="G153" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -3637,19 +3698,19 @@
         <v>226</v>
       </c>
       <c r="C154" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D154" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E154">
-        <v>141</v>
+        <v>303</v>
       </c>
       <c r="F154">
-        <v>141</v>
+        <v>303</v>
       </c>
       <c r="G154" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -3657,19 +3718,19 @@
         <v>227</v>
       </c>
       <c r="C155" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D155" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E155">
-        <v>303</v>
+        <v>253</v>
       </c>
       <c r="F155">
-        <v>303</v>
+        <v>253</v>
       </c>
       <c r="G155" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -3677,19 +3738,19 @@
         <v>228</v>
       </c>
       <c r="C156" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D156" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E156">
-        <v>253</v>
+        <v>111</v>
       </c>
       <c r="F156">
-        <v>253</v>
+        <v>111</v>
       </c>
       <c r="G156" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -3697,19 +3758,19 @@
         <v>229</v>
       </c>
       <c r="C157" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D157" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E157">
-        <v>111</v>
+        <v>93.1</v>
       </c>
       <c r="F157">
-        <v>111</v>
+        <v>93.1</v>
       </c>
       <c r="G157" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -3717,19 +3778,19 @@
         <v>230</v>
       </c>
       <c r="C158" t="s">
-        <v>348</v>
-      </c>
-      <c r="D158" t="s">
-        <v>131</v>
+        <v>132</v>
+      </c>
+      <c r="D158">
+        <v>1</v>
       </c>
       <c r="E158">
-        <v>93.1</v>
+        <v>7.31</v>
       </c>
       <c r="F158">
-        <v>93.1</v>
+        <v>7.31</v>
       </c>
       <c r="G158" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -3737,19 +3798,16 @@
         <v>231</v>
       </c>
       <c r="C159" t="s">
-        <v>133</v>
-      </c>
-      <c r="D159">
-        <v>1</v>
-      </c>
-      <c r="E159">
-        <v>7.31</v>
-      </c>
-      <c r="F159">
-        <v>7.31</v>
+        <v>2</v>
+      </c>
+      <c r="D159" t="s">
+        <v>2</v>
+      </c>
+      <c r="F159" t="s">
+        <v>2</v>
       </c>
       <c r="G159" t="s">
-        <v>134</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -3769,21 +3827,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B161" t="s">
-        <v>233</v>
-      </c>
-      <c r="C161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D161" t="s">
-        <v>2</v>
-      </c>
-      <c r="F161" t="s">
-        <v>2</v>
-      </c>
-      <c r="G161" t="s">
-        <v>2</v>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B163" t="s">
+        <v>352</v>
+      </c>
+      <c r="C163" t="s">
+        <v>353</v>
+      </c>
+      <c r="D163">
+        <v>1</v>
+      </c>
+      <c r="E163">
+        <v>190.59</v>
+      </c>
+      <c r="F163">
+        <v>190.59</v>
+      </c>
+      <c r="G163" t="s">
+        <v>354</v>
       </c>
     </row>
   </sheetData>
